--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,49 +927,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135077155</v>
+        <v>136650823</v>
       </c>
       <c r="B4" t="n">
-        <v>56840</v>
+        <v>9417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>101246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619655</v>
+        <v>619557</v>
       </c>
       <c r="R4" t="n">
-        <v>6353694</v>
+        <v>6353619</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,22 +996,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>levande hane</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,27 +1031,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135077155</t>
+          <t>https://artportalen.se/Sighting/136650823</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123873899</v>
+        <v>136651039</v>
       </c>
       <c r="B5" t="n">
-        <v>58790</v>
+        <v>9417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>101246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,25 +1076,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619655</v>
+        <v>619548</v>
       </c>
       <c r="R5" t="n">
-        <v>6353694</v>
+        <v>6353645</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1117,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Samtldigt satt detta exemplar ovanför på vårt fönster. Levande hane</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,56 +1146,55 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/136651039</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103079905</v>
+        <v>136651049</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>9417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1193,17 +1204,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619653</v>
+        <v>619551</v>
       </c>
       <c r="R6" t="n">
-        <v>6353426</v>
+        <v>6353640</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,19 +1236,29 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Detta exemplar låg under vårt hus samtligt på nästa exemplar. Hane.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,73 +1273,66 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/136651049</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103079906</v>
+        <v>135077155</v>
       </c>
       <c r="B7" t="n">
-        <v>106813</v>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619707</v>
+        <v>619655</v>
       </c>
       <c r="R7" t="n">
-        <v>6353508</v>
+        <v>6353694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,19 +1354,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,73 +1386,70 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103079907</v>
+        <v>123873899</v>
       </c>
       <c r="B8" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619649</v>
+        <v>619655</v>
       </c>
       <c r="R8" t="n">
-        <v>6353533</v>
+        <v>6353694</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,19 +1471,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,34 +1497,31 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103079908</v>
+        <v>103079905</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1542,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619619</v>
+        <v>619653</v>
       </c>
       <c r="R9" t="n">
-        <v>6353564</v>
+        <v>6353426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,17 +1590,17 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,13 +1630,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103079909</v>
+        <v>103079906</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1657,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619688</v>
+        <v>619707</v>
       </c>
       <c r="R10" t="n">
-        <v>6353553</v>
+        <v>6353508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,17 +1705,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,13 +1745,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103079921</v>
+        <v>103079907</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1772,10 +1790,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619624</v>
+        <v>619649</v>
       </c>
       <c r="R11" t="n">
-        <v>6353626</v>
+        <v>6353533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,17 +1820,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,13 +1860,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103081016</v>
+        <v>103079908</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1887,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619738</v>
+        <v>619619</v>
       </c>
       <c r="R12" t="n">
-        <v>6353522</v>
+        <v>6353564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,17 +1935,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,7 +1965,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1957,13 +1975,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103081026</v>
+        <v>103079909</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2002,10 +2020,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619639</v>
+        <v>619688</v>
       </c>
       <c r="R13" t="n">
-        <v>6353675</v>
+        <v>6353553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,17 +2050,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,7 +2080,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2072,13 +2090,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103178444</v>
+        <v>103079921</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2117,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619676</v>
+        <v>619624</v>
       </c>
       <c r="R14" t="n">
-        <v>6353448</v>
+        <v>6353626</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,17 +2165,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,13 +2205,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103178445</v>
+        <v>103081016</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2232,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619687</v>
+        <v>619738</v>
       </c>
       <c r="R15" t="n">
-        <v>6353463</v>
+        <v>6353522</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2280,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2292,7 +2310,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2302,13 +2320,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103178446</v>
+        <v>103081026</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2347,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619706</v>
+        <v>619639</v>
       </c>
       <c r="R16" t="n">
-        <v>6353481</v>
+        <v>6353675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,17 +2395,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2425,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2417,13 +2435,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103178452</v>
+        <v>103178444</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2462,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619614</v>
+        <v>619676</v>
       </c>
       <c r="R17" t="n">
-        <v>6353646</v>
+        <v>6353448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,17 +2510,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,13 +2550,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103178453</v>
+        <v>103178445</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2577,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619658</v>
+        <v>619687</v>
       </c>
       <c r="R18" t="n">
-        <v>6353642</v>
+        <v>6353463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,17 +2625,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,13 +2665,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103178454</v>
+        <v>103178446</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2692,10 +2710,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619633</v>
+        <v>619706</v>
       </c>
       <c r="R19" t="n">
-        <v>6353676</v>
+        <v>6353481</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2722,17 +2740,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,6 +2779,351 @@
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178446</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103178452</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>619614</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6353646</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178452</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103178453</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>619658</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6353642</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -2786,6 +3149,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,49 +1290,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135077155</v>
+        <v>136687600</v>
       </c>
       <c r="B7" t="n">
-        <v>56840</v>
+        <v>9417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>101246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619655</v>
+        <v>619547</v>
       </c>
       <c r="R7" t="n">
-        <v>6353694</v>
+        <v>6353626</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,22 +1359,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Levande hona</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,51 +1394,47 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135077155</t>
+          <t>https://artportalen.se/Sighting/136687600</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B8" t="n">
-        <v>58790</v>
+        <v>56840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1473,22 +1477,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1501,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1515,58 +1518,59 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B9" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R9" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,19 +1592,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,34 +1618,31 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1675,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R10" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1711,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1745,13 +1751,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1790,10 +1796,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R11" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,17 +1826,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,13 +1866,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1905,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R12" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1941,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1975,13 +1981,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2020,10 +2026,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R13" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2056,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2090,13 +2096,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2135,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R14" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,17 +2171,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,13 +2211,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2250,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R15" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,17 +2286,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,7 +2316,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2320,13 +2326,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2365,10 +2371,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R16" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,17 +2401,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,13 +2441,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2480,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R17" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,17 +2516,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,7 +2546,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2550,13 +2556,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2595,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R18" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2625,7 +2631,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2665,13 +2671,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2710,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R19" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2740,7 +2746,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2780,13 +2786,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B20" t="n">
         <v>106813</v>
@@ -2825,10 +2831,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R20" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,17 +2861,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,13 +2901,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B21" t="n">
         <v>106813</v>
@@ -2940,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R21" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2970,7 +2976,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3010,13 +3016,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178452</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B22" t="n">
         <v>106813</v>
@@ -3055,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R22" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,7 +3091,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3124,6 +3130,121 @@
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -3152,6 +3273,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,49 +1411,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135077155</v>
+        <v>136773479</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>9417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>101246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619655</v>
+        <v>619548</v>
       </c>
       <c r="R8" t="n">
-        <v>6353694</v>
+        <v>6353632</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,22 +1480,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kröp på vår veranda igår kväll. Hane.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,51 +1515,47 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135077155</t>
+          <t>https://artportalen.se/Sighting/136773479</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B9" t="n">
-        <v>58790</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1594,22 +1598,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,7 +1622,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1636,58 +1639,59 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B10" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R10" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,19 +1713,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,34 +1739,31 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1796,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R11" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1832,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1866,13 +1872,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1911,10 +1917,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R12" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,17 +1947,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,13 +1987,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2026,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R13" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2062,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2096,13 +2102,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2141,10 +2147,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R14" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2177,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2211,13 +2217,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2256,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R15" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,17 +2292,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,13 +2332,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2371,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R16" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,17 +2407,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,7 +2437,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2441,13 +2447,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2486,10 +2492,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R17" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,17 +2522,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,13 +2562,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2601,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R18" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,17 +2637,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,7 +2667,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2671,13 +2677,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2716,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R19" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,7 +2752,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2786,13 +2792,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B20" t="n">
         <v>106813</v>
@@ -2831,10 +2837,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R20" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,7 +2867,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2901,13 +2907,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B21" t="n">
         <v>106813</v>
@@ -2946,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R21" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2976,17 +2982,17 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,13 +3022,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B22" t="n">
         <v>106813</v>
@@ -3061,10 +3067,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R22" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3091,7 +3097,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3131,13 +3137,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178452</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B23" t="n">
         <v>106813</v>
@@ -3176,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R23" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3212,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3245,6 +3251,121 @@
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -3274,6 +3395,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,49 +1532,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135077155</v>
+        <v>136815470</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>9417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>101246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 242, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619655</v>
+        <v>619500</v>
       </c>
       <c r="R9" t="n">
-        <v>6353694</v>
+        <v>6353558</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,22 +1601,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hittade den på sidan av vägen. Hane utan bakkropp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,51 +1636,47 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135077155</t>
+          <t>https://artportalen.se/Sighting/136815470</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B10" t="n">
-        <v>58790</v>
+        <v>56840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1715,22 +1719,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,7 +1743,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1757,58 +1760,59 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B11" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R11" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,19 +1834,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,34 +1860,31 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1917,10 +1923,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R12" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,7 +1953,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1987,13 +1993,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2032,10 +2038,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R13" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2062,17 +2068,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,13 +2108,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2147,10 +2153,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R14" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,7 +2183,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2217,13 +2223,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2262,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R15" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2292,7 +2298,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2332,13 +2338,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2377,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R16" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,17 +2413,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,13 +2453,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2492,10 +2498,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R17" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,17 +2528,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,7 +2558,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2562,13 +2568,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2607,10 +2613,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R18" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,17 +2643,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,13 +2683,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2722,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R19" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2752,17 +2758,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,7 +2788,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2792,13 +2798,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B20" t="n">
         <v>106813</v>
@@ -2837,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R20" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,7 +2873,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2907,13 +2913,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B21" t="n">
         <v>106813</v>
@@ -2952,10 +2958,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R21" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2982,7 +2988,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3022,13 +3028,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B22" t="n">
         <v>106813</v>
@@ -3067,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R22" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,17 +3103,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,13 +3143,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B23" t="n">
         <v>106813</v>
@@ -3182,10 +3188,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R23" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,7 +3218,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3252,13 +3258,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178452</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B24" t="n">
         <v>106813</v>
@@ -3297,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R24" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3327,7 +3333,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3366,6 +3372,121 @@
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -3396,6 +3517,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,49 +1653,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135077155</v>
+        <v>137006971</v>
       </c>
       <c r="B10" t="n">
-        <v>56840</v>
+        <v>9417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>101246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Enerum, Enerum, Öl</t>
+          <t>Hagskogsvägen 246, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619655</v>
+        <v>619547</v>
       </c>
       <c r="R10" t="n">
-        <v>6353694</v>
+        <v>6353631</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,22 +1722,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En levande och en död hanne i hink från vår stupränna. En skalbagge till i vattnet, en bokoxe. Vi tog upp dem alla från hinken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,51 +1757,47 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Einarsson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135077155</t>
+          <t>https://artportalen.se/Sighting/137006971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B11" t="n">
-        <v>58790</v>
+        <v>56840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1836,22 +1840,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,7 +1864,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1878,58 +1881,59 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B12" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R12" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1951,19 +1955,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,34 +1981,31 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2038,10 +2044,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R13" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,7 +2074,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2108,13 +2114,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2153,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R14" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,17 +2189,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,13 +2229,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2268,10 +2274,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R15" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,7 +2304,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2338,13 +2344,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2383,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R16" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2413,7 +2419,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2453,13 +2459,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2498,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R17" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,17 +2534,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,13 +2574,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2613,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R18" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2643,17 +2649,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,7 +2679,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2683,13 +2689,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2728,10 +2734,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R19" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2758,17 +2764,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,13 +2804,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B20" t="n">
         <v>106813</v>
@@ -2843,10 +2849,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R20" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,17 +2879,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,7 +2909,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2913,13 +2919,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B21" t="n">
         <v>106813</v>
@@ -2958,10 +2964,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R21" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,7 +2994,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3028,13 +3034,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B22" t="n">
         <v>106813</v>
@@ -3073,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R22" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,7 +3109,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3143,13 +3149,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B23" t="n">
         <v>106813</v>
@@ -3188,10 +3194,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R23" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3218,17 +3224,17 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3258,13 +3264,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B24" t="n">
         <v>106813</v>
@@ -3303,10 +3309,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R24" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3333,7 +3339,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3373,13 +3379,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178452</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B25" t="n">
         <v>106813</v>
@@ -3418,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R25" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,7 +3454,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3487,6 +3493,121 @@
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -3518,6 +3639,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136650823</v>
       </c>
       <c r="B4" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>136651039</v>
       </c>
       <c r="B5" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>136651049</v>
       </c>
       <c r="B6" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>136687600</v>
       </c>
       <c r="B7" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>136773479</v>
       </c>
       <c r="B8" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136815470</v>
       </c>
       <c r="B9" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137006971</v>
       </c>
       <c r="B10" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>136773479</v>
       </c>
       <c r="B8" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136815470</v>
       </c>
       <c r="B9" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137006971</v>
       </c>
       <c r="B10" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
